--- a/yanfeng/PKR确认信息/PKR未完成情况（近两周）.xlsx
+++ b/yanfeng/PKR确认信息/PKR未完成情况（近两周）.xlsx
@@ -578,19 +578,16 @@
       <c r="N2" t="inlineStr">
         <is>
           <t xml:space="preserve">最低打分：0；
-Wang Hao23的PKR打分：0；
-Lu Dinghao的PKR打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
 Xu Shirong的PKR打分：0；
-Zhao Kailiang的PKR打分：0；
+Zhao Kailiang的PKR打分：100；
 </t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Wang Hao23的PKR打分：0；
-Lu Dinghao的PKR打分：0；
-Xu Shirong的PKR打分：0；
-Zhao Kailiang的PKR打分：0；</t>
+          <t>Xu Shirong的PKR打分：0；</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -600,11 +597,11 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Total,style="color:
-Wang Hao23,style="color:
-Lu Dinghao,style="color:
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
 Xu Shirong,style="color:
-Zhao Kailiang,style="color:</t>
+Zhao Kailiang,Submitted</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -675,8 +672,8 @@
       <c r="N3" t="inlineStr">
         <is>
           <t xml:space="preserve">最低打分：0；
-Wang Hao23的PKR打分：0；
-Lu Dinghao的PKR打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
 Lu Gongchao的PKR打分：0；
 Xu Shirong的PKR打分：0；
 </t>
@@ -684,9 +681,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Wang Hao23的PKR打分：0；
-Lu Dinghao的PKR打分：0；
-Lu Gongchao的PKR打分：0；
+          <t>Lu Gongchao的PKR打分：0；
 Xu Shirong的PKR打分：0；</t>
         </is>
       </c>
@@ -697,9 +692,9 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>Total,style="color:
-Wang Hao23,style="color:
-Lu Dinghao,style="color:
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
 Lu Gongchao,style="color:
 Xu Shirong,style="color:</t>
         </is>
@@ -772,8 +767,8 @@
       <c r="N4" t="inlineStr">
         <is>
           <t xml:space="preserve">最低打分：0；
-Wang Hao23的PKR打分：0；
-Lu Dinghao的PKR打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
 Lu Gongchao的PKR打分：0；
 Xu Shirong的PKR打分：0；
 </t>
@@ -781,9 +776,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Wang Hao23的PKR打分：0；
-Lu Dinghao的PKR打分：0；
-Lu Gongchao的PKR打分：0；
+          <t>Lu Gongchao的PKR打分：0；
 Xu Shirong的PKR打分：0；</t>
         </is>
       </c>
@@ -794,9 +787,9 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>Total,style="color:
-Wang Hao23,style="color:
-Lu Dinghao,style="color:
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
 Lu Gongchao,style="color:
 Xu Shirong,style="color:</t>
         </is>
@@ -867,6 +860,96 @@
         </is>
       </c>
       <c r="N5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Lu Gongchao的PKR打分：0；
+Xu Shirong的PKR打分：100；
+</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Lu Gongchao的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>本周</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
+Lu Gongchao,style="color:
+Xu Shirong,Submitted</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>30034480-EBP</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>30034480-2028,AP,Toyota,780B,Spraying,260086,T,Equipment</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Toyota</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Gong Shengchao_龚胜超(ugons034)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Chen Ziyi01_陈子翌(uchez443)</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Phase0</t>
+        </is>
+      </c>
+      <c r="H6" s="1" t="n">
+        <v>46138</v>
+      </c>
+      <c r="I6" s="1" t="n">
+        <v>46166</v>
+      </c>
+      <c r="J6" s="1" t="n">
+        <v>46197</v>
+      </c>
+      <c r="K6" s="1" t="n">
+        <v>46227</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Phase 2 Gate Exit-DVR</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
         <is>
           <t xml:space="preserve">最低打分：0；
 Wang Hao23的PKR打分：100；
@@ -876,19 +959,19 @@
 </t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Lu Dinghao的PKR打分：0；
 Lu Gongchao的PKR打分：0；
 Xu Shirong的PKR打分：0；</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>本周</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Total,Submitted
 Wang Hao23,Submitted
@@ -897,99 +980,6 @@
 Xu Shirong,style="color:</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>未评分(工程师)</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>30034480-EBP</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>30034480-2028,AP,Toyota,780B,Spraying,260086,T,Equipment</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Toyota</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Gong Shengchao_龚胜超(ugons034)</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Chen Ziyi01_陈子翌(uchez443)</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Phase0</t>
-        </is>
-      </c>
-      <c r="H6" s="1" t="n">
-        <v>46138</v>
-      </c>
-      <c r="I6" s="1" t="n">
-        <v>46166</v>
-      </c>
-      <c r="J6" s="1" t="n">
-        <v>46197</v>
-      </c>
-      <c r="K6" s="1" t="n">
-        <v>46227</v>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>Phase 2 Gate Exit-DVR</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">最低打分：0；
-Wang Hao23的PKR打分：0；
-Lu Dinghao的PKR打分：0；
-Lu Gongchao的PKR打分：0；
-Xu Shirong的PKR打分：0；
-</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>Wang Hao23的PKR打分：0；
-Lu Dinghao的PKR打分：0；
-Lu Gongchao的PKR打分：0；
-Xu Shirong的PKR打分：0；</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>下周</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>Total,style="color:
-Wang Hao23,style="color:
-Lu Dinghao,style="color:
-Lu Gongchao,style="color:
-Xu Shirong,style="color:</t>
-        </is>
-      </c>
       <c r="R6" t="inlineStr">
         <is>
           <t>未评分(工程师)</t>
@@ -1054,8 +1044,8 @@
       <c r="N7" t="inlineStr">
         <is>
           <t xml:space="preserve">最低打分：0；
-Wang Hao23的PKR打分：0；
-Lu Dinghao的PKR打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
 Lu Gongchao的PKR打分：0；
 Xu Shirong的PKR打分：0；
 </t>
@@ -1063,9 +1053,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Wang Hao23的PKR打分：0；
-Lu Dinghao的PKR打分：0；
-Lu Gongchao的PKR打分：0；
+          <t>Lu Gongchao的PKR打分：0；
 Xu Shirong的PKR打分：0；</t>
         </is>
       </c>
@@ -1076,9 +1064,9 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Total,style="color:
-Wang Hao23,style="color:
-Lu Dinghao,style="color:
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
 Lu Gongchao,style="color:
 Xu Shirong,style="color:</t>
         </is>
@@ -1147,7 +1135,7 @@
       <c r="N8" t="inlineStr">
         <is>
           <t xml:space="preserve">最低打分：0；
-Wang Hao23的PKR打分：0；
+Wang Hao23的PKR打分：100；
 Lu Dinghao的PKR打分：0；
 Xu Shirong的PKR打分：0；
 Zhao Kailiang的PKR打分：0；
@@ -1156,8 +1144,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Wang Hao23的PKR打分：0；
-Lu Dinghao的PKR打分：0；
+          <t>Lu Dinghao的PKR打分：0；
 Xu Shirong的PKR打分：0；
 Zhao Kailiang的PKR打分：0；</t>
         </is>
@@ -1169,8 +1156,8 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Total,style="color:
-Wang Hao23,style="color:
+          <t>Total,Submitted
+Wang Hao23,Submitted
 Lu Dinghao,style="color:
 Xu Shirong,style="color:
 Zhao Kailiang,style="color:</t>
@@ -1238,192 +1225,6 @@
         </is>
       </c>
       <c r="N9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">最低打分：0；
-Wang Hao23的PKR打分：0；
-Lu Dinghao的PKR打分：0；
-Xu Shirong的PKR打分：0；
-Zhao Kailiang的PKR打分：0；
-</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>Wang Hao23的PKR打分：0；
-Lu Dinghao的PKR打分：0；
-Xu Shirong的PKR打分：0；
-Zhao Kailiang的PKR打分：0；</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>下周</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>Total,style="color:
-Wang Hao23,style="color:
-Lu Dinghao,style="color:
-Xu Shirong,style="color:
-Zhao Kailiang,style="color:</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>未评分(工程师)</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>30033376-EBP</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>30033376-2026,AP,Huawei Anhui,F05&amp;F03,Assembly,260031,T,Equipment</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Huawei Anhui</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Meng Zibing_孟子冰(umenz002)</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Xu Shirong_徐时荣(uxuxs004)</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Phase 2 Concept Definition</t>
-        </is>
-      </c>
-      <c r="H10" s="1" t="n">
-        <v>46101</v>
-      </c>
-      <c r="I10" s="1" t="n">
-        <v>46142</v>
-      </c>
-      <c r="J10" s="1" t="n">
-        <v>46163</v>
-      </c>
-      <c r="K10" s="1" t="n">
-        <v>46203</v>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>2026-12-31</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>Phase 3 Gate Exit-FPR</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">最低打分：0；
-Wang Hao23的PKR打分：0；
-Lu Dinghao的PKR打分：0；
-Xu Shirong的PKR打分：0；
-Zhao Kailiang的PKR打分：0；
-</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>Wang Hao23的PKR打分：0；
-Lu Dinghao的PKR打分：0；
-Xu Shirong的PKR打分：0；
-Zhao Kailiang的PKR打分：0；</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>下周</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>Total,style="color:
-Wang Hao23,style="color:
-Lu Dinghao,style="color:
-Xu Shirong,style="color:
-Zhao Kailiang,style="color:</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>未评分(工程师)</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>30033375-EBP</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>30033375-2026,AP,Huawei Anhui,F05&amp;F03,Assembly,260032，T,Equipment</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Huawei Anhui</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Meng Zibing_孟子冰(umenz002)</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Xu Shirong_徐时荣(uxuxs004)</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Phase 2 Concept Definition</t>
-        </is>
-      </c>
-      <c r="H11" s="1" t="n">
-        <v>46111</v>
-      </c>
-      <c r="I11" s="1" t="n">
-        <v>46142</v>
-      </c>
-      <c r="J11" s="1" t="n">
-        <v>46161</v>
-      </c>
-      <c r="K11" s="1" t="n">
-        <v>46203</v>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>2026-12-30</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>Phase 3 Gate Exit-FPR</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
         <is>
           <t xml:space="preserve">最低打分：0；
 Wang Hao23的PKR打分：100；
@@ -1433,18 +1234,18 @@
 </t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Xu Shirong的PKR打分：0；
 Zhao Kailiang的PKR打分：0；</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>下周</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Total,Submitted
 Wang Hao23,Submitted
@@ -1453,6 +1254,186 @@
 Zhao Kailiang,style="color:</t>
         </is>
       </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>30033376-EBP</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>30033376-2026,AP,Huawei Anhui,F05&amp;F03,Assembly,260031,T,Equipment</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Huawei Anhui</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Meng Zibing_孟子冰(umenz002)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Phase 2 Concept Definition</t>
+        </is>
+      </c>
+      <c r="H10" s="1" t="n">
+        <v>46101</v>
+      </c>
+      <c r="I10" s="1" t="n">
+        <v>46142</v>
+      </c>
+      <c r="J10" s="1" t="n">
+        <v>46163</v>
+      </c>
+      <c r="K10" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Phase 3 Gate Exit-FPR</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Xu Shirong的PKR打分：100；
+Zhao Kailiang的PKR打分：0；
+</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Zhao Kailiang的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
+Xu Shirong,Submitted
+Zhao Kailiang,style="color:</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>30033375-EBP</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>30033375-2026,AP,Huawei Anhui,F05&amp;F03,Assembly,260032，T,Equipment</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Huawei Anhui</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Meng Zibing_孟子冰(umenz002)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Phase 2 Concept Definition</t>
+        </is>
+      </c>
+      <c r="H11" s="1" t="n">
+        <v>46111</v>
+      </c>
+      <c r="I11" s="1" t="n">
+        <v>46142</v>
+      </c>
+      <c r="J11" s="1" t="n">
+        <v>46161</v>
+      </c>
+      <c r="K11" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>2026-12-30</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Phase 3 Gate Exit-FPR</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Xu Shirong的PKR打分：100；
+Zhao Kailiang的PKR打分：0；
+</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Zhao Kailiang的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
+Xu Shirong,Submitted
+Zhao Kailiang,style="color:</t>
+        </is>
+      </c>
       <c r="R11" t="inlineStr">
         <is>
           <t>未评分(工程师)</t>
@@ -1519,15 +1500,14 @@
           <t xml:space="preserve">最低打分：0；
 Wang Hao23的PKR打分：100；
 Lu Dinghao的PKR打分：100；
-Xu Shirong的PKR打分：0；
+Xu Shirong的PKR打分：100；
 Zhao Kailiang的PKR打分：0；
 </t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Xu Shirong的PKR打分：0；
-Zhao Kailiang的PKR打分：0；</t>
+          <t>Zhao Kailiang的PKR打分：0；</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1540,7 +1520,7 @@
           <t>Total,Submitted
 Wang Hao23,Submitted
 Lu Dinghao,Submitted
-Xu Shirong,style="color:
+Xu Shirong,Submitted
 Zhao Kailiang,style="color:</t>
         </is>
       </c>
@@ -1608,19 +1588,16 @@
       <c r="N13" t="inlineStr">
         <is>
           <t xml:space="preserve">最低打分：0；
-Wang Hao23的PKR打分：0；
-Lu Dinghao的PKR打分：0；
-Xu Shirong的PKR打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Xu Shirong的PKR打分：100；
 Zhao Kailiang的PKR打分：0；
 </t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Wang Hao23的PKR打分：0；
-Lu Dinghao的PKR打分：0；
-Xu Shirong的PKR打分：0；
-Zhao Kailiang的PKR打分：0；</t>
+          <t>Zhao Kailiang的PKR打分：0；</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1630,10 +1607,10 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Total,style="color:
-Wang Hao23,style="color:
-Lu Dinghao,style="color:
-Xu Shirong,style="color:
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
+Xu Shirong,Submitted
 Zhao Kailiang,style="color:</t>
         </is>
       </c>
@@ -1701,19 +1678,16 @@
       <c r="N14" t="inlineStr">
         <is>
           <t xml:space="preserve">最低打分：0；
-Wang Hao23的PKR打分：0；
-Lu Dinghao的PKR打分：0；
-Xu Shirong的PKR打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Xu Shirong的PKR打分：100；
 Zhao Kailiang的PKR打分：0；
 </t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Wang Hao23的PKR打分：0；
-Lu Dinghao的PKR打分：0；
-Xu Shirong的PKR打分：0；
-Zhao Kailiang的PKR打分：0；</t>
+          <t>Zhao Kailiang的PKR打分：0；</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1723,10 +1697,10 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Total,style="color:
-Wang Hao23,style="color:
-Lu Dinghao,style="color:
-Xu Shirong,style="color:
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
+Xu Shirong,Submitted
 Zhao Kailiang,style="color:</t>
         </is>
       </c>

--- a/yanfeng/PKR确认信息/PKR未完成情况（近两周）.xlsx
+++ b/yanfeng/PKR确认信息/PKR未完成情况（近两周）.xlsx
@@ -16,10 +16,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -49,9 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S3"/>
+  <dimension ref="A1:S7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -520,180 +516,615 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>30035325-EBP</t>
+          <t>30033404-EBP</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>30035325-2026,AP,SERES Motors,遮阳板,1200压机,260145,1M,Equipment</t>
+          <t>30033404-2026,AP,VW Group,VW426-DP,Lamination,260033,M,Equipment</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SERES Motors</t>
+          <t>VW Group</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Meng Zibing_孟子冰(umenz002)</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
+          <t>Gong Shengchao_龚胜超(ugons034)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Huang Linjian_黄琳健(uhual254)</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
+          <t>Phase 4 Manufacturing Development</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Phase 4 Gate Exit-CPA</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：0；
+Lu Gongchao的PKR打分：0；
+Xu Shirong的PKR打分：0；
+</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Lu Dinghao的PKR打分：0；
+Lu Gongchao的PKR打分：0；
+Xu Shirong的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,style="color:
+Lu Gongchao,style="color:
+Xu Shirong,style="color:</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>30033723-EBP</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>30033723-2026,AP,VW Group,VW426 PAB Chute Cell CI,260042,M,Equipment</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>VW Group</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Gong Shengchao_龚胜超(ugons034)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Wei Shaoguan_韦少官(uweis086)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>Phase 2 Concept Definition</t>
         </is>
       </c>
-      <c r="H2" s="1" t="n">
-        <v>46162</v>
-      </c>
-      <c r="I2" s="1" t="n">
-        <v>46164</v>
-      </c>
-      <c r="J2" s="1" t="n">
-        <v>46175</v>
-      </c>
-      <c r="K2" s="1" t="n">
-        <v>46203</v>
-      </c>
-      <c r="L2" s="1" t="n">
-        <v>46387</v>
-      </c>
-      <c r="M2" t="inlineStr">
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>Phase 3 Gate Exit-FPR</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：100；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Xu Shirong的PKR打分：100；
+Zhao Kailiang的PKR打分：100；
+</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>本周</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
+Xu Shirong,Submitted
+Zhao Kailiang,Submitted</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>未确认(Cao Liang)</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>30033578-EBP</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>30033578-2026,AP,Tes,TBD_Click Rim, Lami, 260050, T,Equipment</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Tes</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Zou Chengcheng_邹成成(uzouc016)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Zhou Huasheng_周华盛(uzhoh176)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Phase 3 Design Feasibility</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Phase 3 Gate Exit-FPR</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：0；
+Lu Dinghao的PKR打分：0；
+Lu Gongchao的PKR打分：0；
+Xu Shirong的PKR打分：0；
+</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Wang Hao23的PKR打分：0；
+Lu Dinghao的PKR打分：0；
+Lu Gongchao的PKR打分：0；
+Xu Shirong的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Total,style="color:
+Wang Hao23,style="color:
+Lu Dinghao,style="color:
+Lu Gongchao,style="color:
+Xu Shirong,style="color:</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>30035089-EBP</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>30035089-2026,AP,SAIC-GM,E2LB-2-IP, Automation, 260129, M,Equipment</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>SAIC-GM</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Zou Chengcheng_邹成成(uzouc016)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Wang Xiaoyu03_王晓宇(uwanx1357)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Phase 3 Design Feasibility</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Phase 4 Gate Exit-CPA</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Xu Shirong的PKR打分：0；
+Zhao Kailiang的PKR打分：0；
+</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Xu Shirong的PKR打分：0；
+Zhao Kailiang的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
+Xu Shirong,style="color:
+Zhao Kailiang,style="color:</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>30034166-EBP</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>30034166-2026,AP,SAIC-GM,C1UL-2,CNSL,Lamination,260073,T,Equipment</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>SAIC-GM</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Shang Bing_尚兵(ushab007)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Fan Aiqiang01_樊爱强(ufana018)</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Phase 2 Concept Definition</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Phase 2 Gate Exit-DVR</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
         <is>
           <t xml:space="preserve">最低打分：0；
 Wang Hao23的PKR打分：100；
 Lu Dinghao的PKR打分：100；
 Lu Gongchao的PKR打分：0；
-Xu Shirong的PKR打分：0；
+Xu Shirong的PKR打分：100；
 </t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>Lu Gongchao的PKR打分：0；
-Xu Shirong的PKR打分：0；</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Lu Gongchao的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
         <is>
           <t>下周</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Total,Submitted
 Wang Hao23,Submitted
 Lu Dinghao,Submitted
 Lu Gongchao,style="color:
-Xu Shirong,style="color:</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
+Xu Shirong,Submitted</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
         <is>
           <t>未评分(工程师)</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>30034746-EBP</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>30034746-2026,AP,Huawei Anhui,X90-DP,260115,glue spray,M,Equipment</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Huawei Anhui</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>30035209-EBP</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>30035209-2026,AP,Jianghuai,C673-DP,Foam sticking,T,Equipment</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Jianghuai</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
         <is>
           <t>Shang Bing_尚兵(ushab007)</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Cheng Debao_程德宝(uched025)</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Chen Zhibin01_陈志斌(uchez368)</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>Xu Shirong_徐时荣(uxuxs004)</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Phase 2 Concept Definition</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="n">
-        <v>46166</v>
-      </c>
-      <c r="I3" s="1" t="n">
-        <v>46165</v>
-      </c>
-      <c r="J3" s="1" t="n">
-        <v>46179</v>
-      </c>
-      <c r="K3" s="1" t="n">
-        <v>46221</v>
-      </c>
-      <c r="L3" s="1" t="n">
-        <v>46655</v>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Phase 3 Gate Exit-FPR</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Phase 1 Quotation</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>2027-10-31</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Phase 2 Gate Exit-DVR</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
         <is>
           <t xml:space="preserve">最低打分：0；
-Wang Hao23的PKR打分：100；
-Lu Dinghao的PKR打分：100；
-Lu Gongchao的PKR打分：0；
+Wang Hao23的PKR打分：0；
+Lu Dinghao的PKR打分：0；
 Xu Shirong的PKR打分：0；
+Zhao Kailiang的PKR打分：0；
 </t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>Lu Gongchao的PKR打分：0；
-Xu Shirong的PKR打分：0；</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Wang Hao23的PKR打分：0；
+Lu Dinghao的PKR打分：0；
+Xu Shirong的PKR打分：0；
+Zhao Kailiang的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
         <is>
           <t>下周</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>Total,Submitted
-Wang Hao23,Submitted
-Lu Dinghao,Submitted
-Lu Gongchao,style="color:
-Xu Shirong,style="color:</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Total,style="color:
+Wang Hao23,style="color:
+Lu Dinghao,style="color:
+Xu Shirong,style="color:
+Zhao Kailiang,style="color:</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
         <is>
           <t>未评分(工程师)</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/yanfeng/PKR确认信息/PKR未完成情况（近两周）.xlsx
+++ b/yanfeng/PKR确认信息/PKR未完成情况（近两周）.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S7"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -576,416 +576,6 @@
         </is>
       </c>
       <c r="N2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">最低打分：0；
-Wang Hao23的PKR打分：100；
-Lu Dinghao的PKR打分：0；
-Lu Gongchao的PKR打分：0；
-Xu Shirong的PKR打分：0；
-</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>Lu Dinghao的PKR打分：0；
-Lu Gongchao的PKR打分：0；
-Xu Shirong的PKR打分：0；</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>下周</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>Total,Submitted
-Wang Hao23,Submitted
-Lu Dinghao,style="color:
-Lu Gongchao,style="color:
-Xu Shirong,style="color:</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>未评分(工程师)</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>30033723-EBP</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>30033723-2026,AP,VW Group,VW426 PAB Chute Cell CI,260042,M,Equipment</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>VW Group</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Gong Shengchao_龚胜超(ugons034)</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Wei Shaoguan_韦少官(uweis086)</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Phase 2 Concept Definition</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Phase 3 Gate Exit-FPR</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">最低打分：100；
-Wang Hao23的PKR打分：100；
-Lu Dinghao的PKR打分：100；
-Xu Shirong的PKR打分：100；
-Zhao Kailiang的PKR打分：100；
-</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>完成</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>本周</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>Total,Submitted
-Wang Hao23,Submitted
-Lu Dinghao,Submitted
-Xu Shirong,Submitted
-Zhao Kailiang,Submitted</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>未确认(Cao Liang)</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>30033578-EBP</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>30033578-2026,AP,Tes,TBD_Click Rim, Lami, 260050, T,Equipment</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Tes</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Zou Chengcheng_邹成成(uzouc016)</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Zhou Huasheng_周华盛(uzhoh176)</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Xu Shirong_徐时荣(uxuxs004)</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Phase 3 Design Feasibility</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>2026-11-30</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Phase 3 Gate Exit-FPR</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">最低打分：0；
-Wang Hao23的PKR打分：0；
-Lu Dinghao的PKR打分：0；
-Lu Gongchao的PKR打分：0；
-Xu Shirong的PKR打分：0；
-</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>Wang Hao23的PKR打分：0；
-Lu Dinghao的PKR打分：0；
-Lu Gongchao的PKR打分：0；
-Xu Shirong的PKR打分：0；</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>下周</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>Total,style="color:
-Wang Hao23,style="color:
-Lu Dinghao,style="color:
-Lu Gongchao,style="color:
-Xu Shirong,style="color:</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>未评分(工程师)</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>30035089-EBP</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>30035089-2026,AP,SAIC-GM,E2LB-2-IP, Automation, 260129, M,Equipment</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>SAIC-GM</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Zou Chengcheng_邹成成(uzouc016)</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Wang Xiaoyu03_王晓宇(uwanx1357)</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Xu Shirong_徐时荣(uxuxs004)</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Phase 3 Design Feasibility</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2026-05-16</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>2026-05-23</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>2026-10-31</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Phase 4 Gate Exit-CPA</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">最低打分：0；
-Wang Hao23的PKR打分：100；
-Lu Dinghao的PKR打分：100；
-Xu Shirong的PKR打分：0；
-Zhao Kailiang的PKR打分：0；
-</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>Xu Shirong的PKR打分：0；
-Zhao Kailiang的PKR打分：0；</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>下周</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>Total,Submitted
-Wang Hao23,Submitted
-Lu Dinghao,Submitted
-Xu Shirong,style="color:
-Zhao Kailiang,style="color:</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>未评分(工程师)</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>30034166-EBP</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>30034166-2026,AP,SAIC-GM,C1UL-2,CNSL,Lamination,260073,T,Equipment</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>SAIC-GM</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Shang Bing_尚兵(ushab007)</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Fan Aiqiang01_樊爱强(ufana018)</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Xu Shirong_徐时荣(uxuxs004)</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Phase 2 Concept Definition</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>Phase 2 Gate Exit-DVR</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
         <is>
           <t xml:space="preserve">最低打分：0；
 Wang Hao23的PKR打分：100；
@@ -995,17 +585,17 @@
 </t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Lu Gongchao的PKR打分：0；</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>下周</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Total,Submitted
 Wang Hao23,Submitted
@@ -1014,117 +604,318 @@
 Xu Shirong,Submitted</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>未评分(工程师)</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>30033578-EBP</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>30033578-2026,AP,Tes,TBD_Click Rim, Lami, 260050, T,Equipment</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Tes</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Zou Chengcheng_邹成成(uzouc016)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Zhou Huasheng_周华盛(uzhoh176)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Phase 3 Design Feasibility</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Phase 3 Gate Exit-FPR</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Lu Gongchao的PKR打分：0；
+Xu Shirong的PKR打分：100；
+</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Lu Gongchao的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
+Lu Gongchao,style="color:
+Xu Shirong,Submitted</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>30034166-EBP</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>30034166-2026,AP,SAIC-GM,C1UL-2,CNSL,Lamination,260073,T,Equipment</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>SAIC-GM</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Shang Bing_尚兵(ushab007)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Fan Aiqiang01_樊爱强(ufana018)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Phase 2 Concept Definition</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Phase 2 Gate Exit-DVR</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Lu Gongchao的PKR打分：0；
+Xu Shirong的PKR打分：100；
+</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Lu Gongchao的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
+Lu Gongchao,style="color:
+Xu Shirong,Submitted</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>30035209-EBP</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>30035209-2026,AP,Jianghuai,C673-DP,Foam sticking,T,Equipment</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Jianghuai</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Shang Bing_尚兵(ushab007)</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Chen Zhibin01_陈志斌(uchez368)</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Xu Shirong_徐时荣(uxuxs004)</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Phase 1 Quotation</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>2026-06-13</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>2026-08-15</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>2027-10-31</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Phase 2 Gate Exit-DVR</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t xml:space="preserve">最低打分：0；
-Wang Hao23的PKR打分：0；
-Lu Dinghao的PKR打分：0；
-Xu Shirong的PKR打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Xu Shirong的PKR打分：100；
 Zhao Kailiang的PKR打分：0；
 </t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>Wang Hao23的PKR打分：0；
-Lu Dinghao的PKR打分：0；
-Xu Shirong的PKR打分：0；
-Zhao Kailiang的PKR打分：0；</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Zhao Kailiang的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
         <is>
           <t>下周</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>Total,style="color:
-Wang Hao23,style="color:
-Lu Dinghao,style="color:
-Xu Shirong,style="color:
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
+Xu Shirong,Submitted
 Zhao Kailiang,style="color:</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>未评分(工程师)</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/yanfeng/PKR确认信息/PKR未完成情况（近两周）.xlsx
+++ b/yanfeng/PKR确认信息/PKR未完成情况（近两周）.xlsx
@@ -516,58 +516,62 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>30033404-EBP</t>
+          <t>30034622-EBP</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>30033404-2026,AP,VW Group,VW426-DP,Lamination,260033,M,Equipment</t>
+          <t>30034622-2026,AP,BYD,Glue,260101,M,Equipment</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VW Group</t>
+          <t>BYD</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Gong Shengchao_龚胜超(ugons034)</t>
+          <t>Shang Bing_尚兵(ushab007)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Huang Linjian_黄琳健(uhual254)</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
+          <t>Chen Jie04_陈洁(uchej018)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phase 4 Manufacturing Development</t>
+          <t>Phase 2 Concept Definition</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2027-09-30</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -614,70 +618,270 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>30033578-EBP</t>
+          <t>30034171-EBP</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>30033578-2026,AP,Tes,TBD_Click Rim, Lami, 260050, T,Equipment</t>
+          <t>30034171-2026,AP,Jianghuai,JHC-sun visor,assy, 260074, NT,Equipment</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Tes</t>
+          <t>Jianghuai</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Zou Chengcheng_邹成成(uzouc016)</t>
+          <t>Wang Baowei_王保卫(uwanb363)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Zhou Huasheng_周华盛(uzhoh176)</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
+          <t>Chen Zhibin01_陈志斌(uchez368)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Phase 3 Design Feasibility</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Phase 3 Gate Exit-FPR</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Xu Shirong的PKR打分：100；
+Zhao Kailiang的PKR打分：0；
+</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Zhao Kailiang的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
+Xu Shirong,Submitted
+Zhao Kailiang,style="color:</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>30034168-EBP</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>30034168-2026,AP,SVW,A-SUV-mirror,assembly,260008,15T,Equipment</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>SVW</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Wang Baowei_王保卫(uwanb363)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Zhou Liwen_周理文(uzhol008)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>Xu Shirong_徐时荣(uxuxs004)</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Phase 3 Design Feasibility</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>2026-11-30</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
         <is>
           <t>Phase 3 Gate Exit-FPR</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Xu Shirong的PKR打分：100；
+Zhao Kailiang的PKR打分：0；
+</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Zhao Kailiang的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
+Xu Shirong,Submitted
+Zhao Kailiang,style="color:</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>30034623-EBP</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>30034623-2026,AP,BYD,Glue,260103,M,Equipment</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>BYD</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Shang Bing_尚兵(ushab007)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Chen Jie04_陈洁(uchej018)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Phase 3 Design Feasibility</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>2027-09-08</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Phase 4 Gate Exit-CPA</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t xml:space="preserve">最低打分：0；
 Wang Hao23的PKR打分：100；
@@ -687,227 +891,23 @@
 </t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Lu Gongchao的PKR打分：0；</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>下周</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Total,Submitted
 Wang Hao23,Submitted
 Lu Dinghao,Submitted
 Lu Gongchao,style="color:
 Xu Shirong,Submitted</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>未评分(工程师)</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>30034166-EBP</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>30034166-2026,AP,SAIC-GM,C1UL-2,CNSL,Lamination,260073,T,Equipment</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>SAIC-GM</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Shang Bing_尚兵(ushab007)</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Fan Aiqiang01_樊爱强(ufana018)</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Xu Shirong_徐时荣(uxuxs004)</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Phase 2 Concept Definition</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Phase 2 Gate Exit-DVR</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">最低打分：0；
-Wang Hao23的PKR打分：100；
-Lu Dinghao的PKR打分：100；
-Lu Gongchao的PKR打分：0；
-Xu Shirong的PKR打分：100；
-</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>Lu Gongchao的PKR打分：0；</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>下周</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>Total,Submitted
-Wang Hao23,Submitted
-Lu Dinghao,Submitted
-Lu Gongchao,style="color:
-Xu Shirong,Submitted</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>未评分(工程师)</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>30035209-EBP</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>30035209-2026,AP,Jianghuai,C673-DP,Foam sticking,T,Equipment</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Jianghuai</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Shang Bing_尚兵(ushab007)</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Chen Zhibin01_陈志斌(uchez368)</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Xu Shirong_徐时荣(uxuxs004)</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Phase 1 Quotation</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>2026-08-15</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>2027-10-31</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Phase 2 Gate Exit-DVR</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">最低打分：0；
-Wang Hao23的PKR打分：100；
-Lu Dinghao的PKR打分：100；
-Xu Shirong的PKR打分：100；
-Zhao Kailiang的PKR打分：0；
-</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>Zhao Kailiang的PKR打分：0；</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>下周</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>Total,Submitted
-Wang Hao23,Submitted
-Lu Dinghao,Submitted
-Xu Shirong,Submitted
-Zhao Kailiang,style="color:</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">

--- a/yanfeng/PKR确认信息/PKR未完成情况（近两周）.xlsx
+++ b/yanfeng/PKR确认信息/PKR未完成情况（近两周）.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S5"/>
+  <dimension ref="A1:S8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -516,67 +516,63 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>30034622-EBP</t>
+          <t>30034480-EBP</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>30034622-2026,AP,BYD,Glue,260101,M,Equipment</t>
+          <t>30034480-2028,AP,Toyota,780B,Spraying,260086,T,Equipment</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>BYD</t>
+          <t>Toyota</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Shang Bing_尚兵(ushab007)</t>
+          <t>Gong Shengchao_龚胜超(ugons034)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Chen Jie04_陈洁(uchej018)</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Xu Shirong_徐时荣(uxuxs004)</t>
-        </is>
-      </c>
+          <t>Chen Ziyi01_陈子翌(uchez443)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phase 2 Concept Definition</t>
+          <t>Phase 3 Design Feasibility</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2027-09-30</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Phase 4 Gate Exit-CPA</t>
+          <t>Phase 3 Gate Exit-FPR</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -618,27 +614,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>30034171-EBP</t>
+          <t>30034479-EBP</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>30034171-2026,AP,Jianghuai,JHC-sun visor,assy, 260074, NT,Equipment</t>
+          <t>30034479-2027,AP,Toyota,780B,Spraying,260085,M,Equipment</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Jianghuai</t>
+          <t>Toyota</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Wang Baowei_王保卫(uwanb363)</t>
+          <t>Gong Shengchao_龚胜超(ugons034)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Chen Zhibin01_陈志斌(uchez368)</t>
+          <t>Chen Jie04_陈洁(uchej018)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -649,27 +645,27 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -678,6 +674,104 @@
         </is>
       </c>
       <c r="N3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Lu Gongchao的PKR打分：0；
+Xu Shirong的PKR打分：100；
+</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Lu Gongchao的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
+Lu Gongchao,style="color:
+Xu Shirong,Submitted</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>30034478-EBP</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>30034478-2026,AP,Toyota,780B-DP, flaming,260080,T,Equipment</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Toyota</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Gong Shengchao_龚胜超(ugons034)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Zhang Shuai27_张帅(uzhas1129)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Phase 3 Design Feasibility</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Phase 3 Gate Exit-FPR</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t xml:space="preserve">最低打分：0；
 Wang Hao23的PKR打分：100；
@@ -687,17 +781,17 @@
 </t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Zhao Kailiang的PKR打分：0；</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>下周</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Total,Submitted
 Wang Hao23,Submitted
@@ -706,80 +800,76 @@
 Zhao Kailiang,style="color:</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>未评分(工程师)</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>30034168-EBP</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>30034168-2026,AP,SVW,A-SUV-mirror,assembly,260008,15T,Equipment</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>SVW</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Wang Baowei_王保卫(uwanb363)</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Zhou Liwen_周理文(uzhol008)</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Xu Shirong_徐时荣(uxuxs004)</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>30034477-EBP</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>30034477-2025,AP,Toyota,780B-DP,Flaming, 260079,M,Equipment</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Toyota</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Gong Shengchao_龚胜超(ugons034)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Huang Linjian_黄琳健(uhual254)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
         <is>
           <t>Phase 3 Design Feasibility</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>2026-07-18</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
         <is>
           <t>Phase 3 Gate Exit-FPR</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t xml:space="preserve">最低打分：0；
 Wang Hao23的PKR打分：100；
@@ -789,17 +879,17 @@
 </t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Zhao Kailiang的PKR打分：0；</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>下周</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Total,Submitted
 Wang Hao23,Submitted
@@ -808,80 +898,80 @@
 Zhao Kailiang,style="color:</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>未评分(工程师)</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>30034623-EBP</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>30034623-2026,AP,BYD,Glue,260103,M,Equipment</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>BYD</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>30034166-EBP</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>30034166-2026,AP,SAIC-GM,C1UL-2,CNSL,Lamination,260073,T,Equipment</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>SAIC-GM</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
         <is>
           <t>Shang Bing_尚兵(ushab007)</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Chen Jie04_陈洁(uchej018)</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Fan Aiqiang01_樊爱强(ufana018)</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>Xu Shirong_徐时荣(uxuxs004)</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>Phase 3 Design Feasibility</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>2027-09-08</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Phase 4 Gate Exit-CPA</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Phase 3 Gate Exit-FPR</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
         <is>
           <t xml:space="preserve">最低打分：0；
 Wang Hao23的PKR打分：100；
@@ -891,17 +981,17 @@
 </t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Lu Gongchao的PKR打分：0；</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>下周</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Total,Submitted
 Wang Hao23,Submitted
@@ -910,12 +1000,216 @@
 Xu Shirong,Submitted</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>未评分(工程师)</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>30035161-EBP</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>30035161-2026,AP,BJEV,X90,Lamination,260132,M,Equipment</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>BJEV</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Shang Bing_尚兵(ushab007)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Chen Jie04_陈洁(uchej018)</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Phase 1 Quotation</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>2027-10-20</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Phase 2 Gate Exit-DVR</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Lu Gongchao的PKR打分：0；
+Xu Shirong的PKR打分：100；
+</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Lu Gongchao的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>本周</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
+Lu Gongchao,style="color:
+Xu Shirong,Submitted</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>30035162-EBP</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>30035162-2026,AP,BJEV,X90,Lamination,260133,M,Equipment</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>BJEV</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Shang Bing_尚兵(ushab007)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Chen Jie04_陈洁(uchej018)</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Phase 1 Quotation</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>2027-10-20</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Phase 2 Gate Exit-DVR</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Lu Gongchao的PKR打分：0；
+Xu Shirong的PKR打分：100；
+</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Lu Gongchao的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
+Lu Gongchao,style="color:
+Xu Shirong,Submitted</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/yanfeng/PKR确认信息/PKR未完成情况（近两周）.xlsx
+++ b/yanfeng/PKR确认信息/PKR未完成情况（近两周）.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S8"/>
+  <dimension ref="A1:S25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -516,63 +516,67 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>30034480-EBP</t>
+          <t>30028719-EBP</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>30034480-2028,AP,Toyota,780B,Spraying,260086,T,Equipment</t>
+          <t>30028719-2025,AP,smartmi,MX11-DAB,Lamination,250188,T,Equipment</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Toyota</t>
+          <t>smartmi</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Gong Shengchao_龚胜超(ugons034)</t>
+          <t>Zou Chengcheng_邹成成(uzouc016)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Chen Ziyi01_陈子翌(uchez443)</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
+          <t>Jin Yulong01_金宇隆(ujiny132)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Liu Cong02_刘聪(uliuc396)</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phase 3 Design Feasibility</t>
+          <t>Phase 4 Manufacturing Development</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Phase 3 Gate Exit-FPR</t>
+          <t>Phase 4 Gate Exit-CPA</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -614,63 +618,67 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>30034479-EBP</t>
+          <t>30032531-EBP</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>30034479-2027,AP,Toyota,780B,Spraying,260085,M,Equipment</t>
+          <t>30032531-2026,AP,SERES Motors,F2N-DAB, Lamination, 250383, T,Equipment</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Toyota</t>
+          <t>SERES Motors</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Gong Shengchao_龚胜超(ugons034)</t>
+          <t>Zou Chengcheng_邹成成(uzouc016)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Chen Jie04_陈洁(uchej018)</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
+          <t>Huang Dongfang01_黄东方(uhuad056)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phase 3 Design Feasibility</t>
+          <t>Phase 4 Manufacturing Development</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Phase 3 Gate Exit-FPR</t>
+          <t>Phase 4 Gate Exit-CPA</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -712,63 +720,63 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>30034478-EBP</t>
+          <t>30033407-EBP</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>30034478-2026,AP,Toyota,780B-DP, flaming,260080,T,Equipment</t>
+          <t>30033407-2026,AP,Huawei Anhui,F05/F03 CNSL,Assembly,260036,M,Equipment</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Toyota</t>
+          <t>Huawei Anhui</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Gong Shengchao_龚胜超(ugons034)</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Zhang Shuai27_张帅(uzhas1129)</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
+          <t>Meng Zibing_孟子冰(umenz002)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phase 3 Design Feasibility</t>
+          <t>Phase 4 Manufacturing Development</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Phase 3 Gate Exit-FPR</t>
+          <t>Phase 4 Gate Exit-CPA</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -810,63 +818,63 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>30034477-EBP</t>
+          <t>30033376-EBP</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>30034477-2025,AP,Toyota,780B-DP,Flaming, 260079,M,Equipment</t>
+          <t>30033376-2026,AP,Huawei Anhui,F05&amp;F03,Assembly,260031,T,Equipment</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Toyota</t>
+          <t>Huawei Anhui</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Gong Shengchao_龚胜超(ugons034)</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Huang Linjian_黄琳健(uhual254)</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
+          <t>Meng Zibing_孟子冰(umenz002)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phase 3 Design Feasibility</t>
+          <t>Phase 4 Manufacturing Development</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Phase 3 Gate Exit-FPR</t>
+          <t>Phase 4 Gate Exit-CPA</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -908,29 +916,25 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>30034166-EBP</t>
+          <t>30033405-EBP</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>30034166-2026,AP,SAIC-GM,C1UL-2,CNSL,Lamination,260073,T,Equipment</t>
+          <t>30033405-2026,AP,Huawei Anhui,F05 IP,Assembly,260038,M,Equipment</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SAIC-GM</t>
+          <t>Huawei Anhui</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Shang Bing_尚兵(ushab007)</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Fan Aiqiang01_樊爱强(ufana018)</t>
-        </is>
-      </c>
+          <t>Meng Zibing_孟子冰(umenz002)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>Xu Shirong_徐时荣(uxuxs004)</t>
@@ -938,40 +942,840 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
+          <t>Phase 4 Manufacturing Development</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Phase 4 Gate Exit-CPA</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Xu Shirong的PKR打分：100；
+Zhao Kailiang的PKR打分：0；
+</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Zhao Kailiang的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
+Xu Shirong,Submitted
+Zhao Kailiang,style="color:</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>30033373-EBP</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>30033373-2026,AP,Huawei Anhui,F03F05,Assembly,260030,T,Equipment</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Huawei Anhui</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Meng Zibing_孟子冰(umenz002)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Phase 4 Manufacturing Development</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Phase 4 Gate Exit-CPA</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Xu Shirong的PKR打分：100；
+Zhao Kailiang的PKR打分：0；
+</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Zhao Kailiang的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
+Xu Shirong,Submitted
+Zhao Kailiang,style="color:</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>30033375-EBP</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>30033375-2026,AP,Huawei Anhui,F05&amp;F03,Assembly,260032，T,Equipment</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Huawei Anhui</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Meng Zibing_孟子冰(umenz002)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Phase 4 Manufacturing Development</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>2026-12-30</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Phase 4 Gate Exit-CPA</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Xu Shirong的PKR打分：100；
+Zhao Kailiang的PKR打分：0；
+</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Zhao Kailiang的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
+Xu Shirong,Submitted
+Zhao Kailiang,style="color:</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>30033409-EBP</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>30033409-2026,AP,Huawei Anhui,F05/F03 CNSL,Assembly,260037,M,Equipment</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Huawei Anhui</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Meng Zibing_孟子冰(umenz002)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
           <t>Phase 3 Design Feasibility</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>2026-12-30</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
         <is>
           <t>Phase 3 Gate Exit-FPR</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Xu Shirong的PKR打分：100；
+Zhao Kailiang的PKR打分：0；
+</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Zhao Kailiang的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
+Xu Shirong,Submitted
+Zhao Kailiang,style="color:</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>30033723-EBP</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>30033723-2026,AP,VW Group,VW426 PAB Chute Cell CI,260042,M,Equipment</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>VW Group</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Gong Shengchao_龚胜超(ugons034)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Wei Shaoguan_韦少官(uweis086)</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Phase 4 Manufacturing Development</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Phase 4 Gate Exit-CPA</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Xu Shirong的PKR打分：100；
+Zhao Kailiang的PKR打分：0；
+</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Zhao Kailiang的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
+Xu Shirong,Submitted
+Zhao Kailiang,style="color:</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>30034473-EBP</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>30034473-2026,AP,SERES Motors,F2N-light,260081,M,Equipment</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>SERES Motors</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Chen Jiarong_陈佳荣(uchej731)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Hao Xiuxia_郝秀霞(uhaox031)</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Phase 4 Manufacturing Development</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>2026-12-10</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Phase 4 Gate Exit-CPA</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Xu Shirong的PKR打分：100；
+Zhao Kailiang的PKR打分：0；
+</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Zhao Kailiang的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
+Xu Shirong,Submitted
+Zhao Kailiang,style="color:</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>30032706-EBP</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>30032706-2025,AP,SERES Motors,A15-mirror, assy, 260006, 15T,Equipment</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>SERES Motors</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Wang Baowei_王保卫(uwanb363)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Wang Wanfang_王万芳(uwanw356)</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Phase 4 Manufacturing Development</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Phase 4 Gate Exit-CPA</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Xu Shirong的PKR打分：100；
+Zhao Kailiang的PKR打分：0；
+</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Zhao Kailiang的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
+Xu Shirong,Submitted
+Zhao Kailiang,style="color:</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>30033461-EBP</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>30033461-2026,AP,SVW,B-SUV-mirror,assy,260041,1M,Equipment</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>SVW</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Wang Baowei_王保卫(uwanb363)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Chen Zhibin01_陈志斌(uchez368)</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Phase 2 Concept Definition</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Phase 3 Gate Exit-FPR</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Xu Shirong的PKR打分：100；
+Zhao Kailiang的PKR打分：0；
+</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Zhao Kailiang的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
+Xu Shirong,Submitted
+Zhao Kailiang,style="color:</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>30034615-EBP</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>30034615-2026,AP,BYD,MR&amp;ST-IP, Glue,260091, M,Equipment</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>BYD</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Yuan Shuai_袁帅(uyuas003)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Chen Jie04_陈洁(uchej018)</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Phase 3 Design Feasibility</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>2026-12-30</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Phase 3 Gate Exit-FPR</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
         <is>
           <t xml:space="preserve">最低打分：0；
 Wang Hao23的PKR打分：100；
@@ -981,17 +1785,17 @@
 </t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>Lu Gongchao的PKR打分：0；</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>下周</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>Total,Submitted
 Wang Hao23,Submitted
@@ -1000,80 +1804,174 @@
 Xu Shirong,Submitted</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t>未评分(工程师)</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>30035161-EBP</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>30035161-2026,AP,BJEV,X90,Lamination,260132,M,Equipment</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>BJEV</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Shang Bing_尚兵(ushab007)</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Chen Jie04_陈洁(uchej018)</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>30030761-EBP</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>30030761-2025,AP,SAIC-VW,VW416-IP,Automatin,250306,M,,Equipment</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>SAIC-VW</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Xia Yang_夏阳(uxiay057)</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Liu Jinghua01_刘璟华(uliuj595)</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
         <is>
           <t>Xu Shirong_徐时荣(uxuxs004)</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>Phase 1 Quotation</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>2027-10-20</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>Phase 2 Gate Exit-DVR</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Phase 3 Gate Exit-FPR</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Xu Shirong的PKR打分：100；
+Zhao Kailiang的PKR打分：0；
+</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Zhao Kailiang的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
+Xu Shirong,Submitted
+Zhao Kailiang,style="color:</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>30035325-EBP</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>30035325-2026,AP,SERES Motors,遮阳板,1200压机,260145,1M,Equipment</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>SERES Motors</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Meng Zibing_孟子冰(umenz002)</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Phase 4 Manufacturing Development</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Phase 4 Gate Exit-CPA</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
         <is>
           <t xml:space="preserve">最低打分：0；
 Wang Hao23的PKR打分：100；
@@ -1083,17 +1981,17 @@
 </t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>Lu Gongchao的PKR打分：0；</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>本周</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
         <is>
           <t>Total,Submitted
 Wang Hao23,Submitted
@@ -1102,80 +2000,80 @@
 Xu Shirong,Submitted</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="R16" t="inlineStr">
         <is>
           <t>未评分(工程师)</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>30035162-EBP</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>30035162-2026,AP,BJEV,X90,Lamination,260133,M,Equipment</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>BJEV</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Shang Bing_尚兵(ushab007)</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Chen Jie04_陈洁(uchej018)</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>30035205-EBP</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>30035205-2027,AP,SERES Motors,E68-DP,lamination,260138,2M,Equipment</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>SERES Motors</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Yuan Shuai_袁帅(uyuas003)</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Huang Linjian_黄琳健(uhual254)</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
         <is>
           <t>Xu Shirong_徐时荣(uxuxs004)</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Phase 1 Quotation</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>2026-07-18</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>2027-10-20</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Phase 2 Concept Definition</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>2026-12-30</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
         <is>
           <t>Phase 2 Gate Exit-DVR</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t xml:space="preserve">最低打分：0；
 Wang Hao23的PKR打分：100；
@@ -1185,17 +2083,17 @@
 </t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>Lu Gongchao的PKR打分：0；</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>下周</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>Total,Submitted
 Wang Hao23,Submitted
@@ -1204,12 +2102,824 @@
 Xu Shirong,Submitted</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="R17" t="inlineStr">
         <is>
           <t>未评分(工程师)</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>30035209-EBP</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>30035209-2026,AP,Jianghuai,C673-DP,Foam sticking,T,Equipment</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Jianghuai</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Shang Bing_尚兵(ushab007)</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Chen Zhibin01_陈志斌(uchez368)</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Phase 2 Concept Definition</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>2027-10-31</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Phase 3 Gate Exit-FPR</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Xu Shirong的PKR打分：100；
+Zhao Kailiang的PKR打分：0；
+</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Zhao Kailiang的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
+Xu Shirong,Submitted
+Zhao Kailiang,style="color:</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>30017341-EBP</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>30017341-2024,AP,BYD,SA5-IP,Lamination,220281,M,Equipment</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>BYD</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Shang Bing_尚兵(ushab007)</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Liu Cong02_刘聪(uliuc396)</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Phase 1 Quotation</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Phase 2 Gate Exit-DVR</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Lu Gongchao的PKR打分：0；
+Xu Shirong的PKR打分：100；
+</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Lu Gongchao的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
+Lu Gongchao,style="color:
+Xu Shirong,Submitted</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>30034578-EBP</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>30034578-2026,AP,BYD,Glue,260093,M,Equipment</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>BYD</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Shang Bing_尚兵(ushab007)</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Chen Jie04_陈洁(uchej018)</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Phase 1 Quotation</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Phase 2 Gate Exit-DVR</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Lu Gongchao的PKR打分：0；
+Xu Shirong的PKR打分：100；
+</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Lu Gongchao的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
+Lu Gongchao,style="color:
+Xu Shirong,Submitted</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>30035208-EBP</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>30035208-2026,AP,Jianghuai,C673-DP,Foam Sticking,260140,M,Equipment</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Jianghuai</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Shang Bing_尚兵(ushab007)</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Chen Zhibin01_陈志斌(uchez368)</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Phase 2 Concept Definition</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>2027-10-29</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Phase 3 Gate Exit-FPR</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Xu Shirong的PKR打分：100；
+Zhao Kailiang的PKR打分：0；
+</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Zhao Kailiang的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
+Xu Shirong,Submitted
+Zhao Kailiang,style="color:</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>30034577-EBP</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>30034577-2026,AP,BYD,EHX,Glue,260088,M,Equipment</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>BYD</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Shang Bing_尚兵(ushab007)</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Chen Jie04_陈洁(uchej018)</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Phase 1 Quotation</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Phase 2 Gate Exit-DVR</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Lu Gongchao的PKR打分：0；
+Xu Shirong的PKR打分：100；
+</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Lu Gongchao的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
+Lu Gongchao,style="color:
+Xu Shirong,Submitted</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>30035188-EBP</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>30035188-2026,AP,smartmi,KUNLUN-light,welding.260135.M,Equipment</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>smartmi</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Chen Jiarong_陈佳荣(uchej731)</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Wei Shaoguan_韦少官(uweis086)</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Phase 1 Quotation</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>2026-12-10</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Phase 2 Gate Exit-DVR</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Xu Shirong的PKR打分：100；
+Zhao Kailiang的PKR打分：0；
+</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Zhao Kailiang的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
+Xu Shirong,Submitted
+Zhao Kailiang,style="color:</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>30035096-EBP</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>30035096-2026,AP,smartmi,F2N-light,welding260130,M,Equipment</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>smartmi</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Chen Jiarong_陈佳荣(uchej731)</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Wei Shaoguan_韦少官(uweis086)</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Phase 1 Quotation</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>2026-12-10</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Phase 2 Gate Exit-DVR</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Xu Shirong的PKR打分：100；
+Zhao Kailiang的PKR打分：0；
+</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Zhao Kailiang的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
+Xu Shirong,Submitted
+Zhao Kailiang,style="color:</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>30035161-EBP</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>30035161-2026,AP,BJEV,X90,Lamination,260132,M,Equipment</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>BJEV</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Shang Bing_尚兵(ushab007)</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Chen Jie04_陈洁(uchej018)</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Phase 1 Quotation</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>2027-10-20</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Phase 3 Gate Exit-FPR</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Lu Gongchao的PKR打分：0；
+Xu Shirong的PKR打分：100；
+</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Lu Gongchao的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
+Lu Gongchao,style="color:
+Xu Shirong,Submitted</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/yanfeng/PKR确认信息/PKR未完成情况（近两周）.xlsx
+++ b/yanfeng/PKR确认信息/PKR未完成情况（近两周）.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S8"/>
+  <dimension ref="A1:S9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -516,295 +516,304 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>30034579-EBP</t>
+          <t>30034171-EBP</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>30034579-2026,AP,BYD,Glue,260095,M,Equipment</t>
+          <t>30034171-2026,AP,Jianghuai,JHC-sun visor,assy, 260074, NT,Equipment</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>BYD</t>
+          <t>Jianghuai</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>Wang Baowei_王保卫(uwanb363)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Chen Zhibin01_陈志斌(uchez368)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Phase 4 Manufacturing Development</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Phase 4 Gate Exit-CPA</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：0；
+Lu Dinghao的PKR打分：100；
+Xu Shirong的PKR打分：0；
+Zhao Kailiang的PKR打分：0；
+</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Wang Hao23的PKR打分：0；
+Xu Shirong的PKR打分：0；
+Zhao Kailiang的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,style="color:
+Lu Dinghao,Submitted
+Xu Shirong,style="color:
+Zhao Kailiang,style="color:</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>30034168-EBP</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>30034168-2026,AP,SVW,A-SUV-mirror,assembly,260008,15T,Equipment</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>SVW</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Wang Baowei_王保卫(uwanb363)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Zhou Liwen_周理文(uzhol008)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Phase 3 Design Feasibility</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Phase 4 Gate Exit-CPA</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Xu Shirong的PKR打分：0；
+Zhao Kailiang的PKR打分：0；
+</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Xu Shirong的PKR打分：0；
+Zhao Kailiang的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
+Xu Shirong,style="color:
+Zhao Kailiang,style="color:</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>30034746-EBP</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>30034746-2026,AP,Huawei Anhui,X90-DP,260115,glue spray,M,Equipment</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Huawei Anhui</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>Shang Bing_尚兵(ushab007)</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Chen Jie04_陈洁(uchej018)</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Cheng Debao_程德宝(uched025)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>Xu Shirong_徐时荣(uxuxs004)</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Phase 2 Concept Definition</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Phase 2 Gate Exit-DVR</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Phase 3 Design Feasibility</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>2027-09-25</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Phase 4 Gate Exit-CPA</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t xml:space="preserve">最低打分：0；
 Wang Hao23的PKR打分：100；
 Lu Dinghao的PKR打分：100；
 Lu Gongchao的PKR打分：0；
-Xu Shirong的PKR打分：100；
+Xu Shirong的PKR打分：0；
 </t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>Lu Gongchao的PKR打分：0；</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Lu Gongchao的PKR打分：0；
+Xu Shirong的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>下周</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Total,Submitted
 Wang Hao23,Submitted
 Lu Dinghao,Submitted
 Lu Gongchao,style="color:
-Xu Shirong,Submitted</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>未评分(工程师)</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>30035236-EBP</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>30035236-2026,NA,Ford,P703-Airbag, assembly, 260142,1T,Equipment</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ford</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Wang Baowei_王保卫(uwanb363)</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Huang Dinghui_黄定辉(uhuad002)</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Phase 1 Quotation</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Phase 2 Gate Exit-DVR</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">最低打分：0；
-Wang Hao23的PKR打分：100；
-Lu Dinghao的PKR打分：100；
-Xu Shirong的PKR打分：100；
-Zhao Kailiang的PKR打分：0；
-</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>Zhao Kailiang的PKR打分：0；</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>下周</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>Total,Submitted
-Wang Hao23,Submitted
-Lu Dinghao,Submitted
-Xu Shirong,Submitted
-Zhao Kailiang,style="color:</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>未评分(工程师)</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>30036184-EBP</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>30036184-2026,AP,JAC-VW,JHB-sunvisor,assem, 260180, 2T,Equipment</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>JAC-VW</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Chen Zhibin01_陈志斌(uchez368)</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Xu Shirong_徐时荣(uxuxs004)</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Phase 1 Quotation</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>2026-07-26</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>2027-01-31</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Phase 2 Gate Exit-DVR</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">最低打分：0；
-Wang Hao23的PKR打分：0；
-Lu Dinghao的PKR打分：0；
-Xu Shirong的PKR打分：0；
-Zhao Kailiang的PKR打分：0；
-</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>Wang Hao23的PKR打分：0；
-Lu Dinghao的PKR打分：0；
-Xu Shirong的PKR打分：0；
-Zhao Kailiang的PKR打分：0；</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>本周</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>Total,style="color:
-Wang Hao23,style="color:
-Lu Dinghao,style="color:
-Xu Shirong,style="color:
-Zhao Kailiang,style="color:</t>
+Xu Shirong,style="color:</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -817,23 +826,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>30033911-EBP</t>
+          <t>30035162-EBP</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>30033911-2026,NA,Stellantis,WL-DP,laminnation,260060,T,Equipment</t>
+          <t>30035162-2026,AP,BJEV,X90,Lamination,260133,M,Equipment</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Stellantis</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>BJEV</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Shang Bing_尚兵(ushab007)</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Jin Yulong01_金宇隆(ujiny132)</t>
+          <t>Chen Jie04_陈洁(uchej018)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -843,58 +856,68 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phase 1 Quotation</t>
+          <t>Phase 2 Concept Definition</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2027-10-20</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Phase 4 Gate Exit-CPA</t>
+          <t>Phase 3 Gate Exit-FPR</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t xml:space="preserve">最低打分：；
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：0；
+Lu Dinghao的PKR打分：100；
+Lu Gongchao的PKR打分：0；
+Xu Shirong的PKR打分：0；
 </t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>完成</t>
+          <t>Wang Hao23的PKR打分：0；
+Lu Gongchao的PKR打分：0；
+Xu Shirong的PKR打分：0；</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>本周</t>
+          <t>下周</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>Total,style="color:</t>
+          <t>Total,Submitted
+Wang Hao23,style="color:
+Lu Dinghao,Submitted
+Lu Gongchao,style="color:
+Xu Shirong,style="color:</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -920,7 +943,11 @@
           <t>Stellantis</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Wang Xiang02_王翔(uwanx029)</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>Jin Yulong01_金宇隆(ujiny132)</t>
@@ -968,7 +995,11 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t xml:space="preserve">最低打分：；
+          <t xml:space="preserve">最低打分：100；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Lu Gongchao的PKR打分：100；
+Xu Shirong的PKR打分：100；
 </t>
         </is>
       </c>
@@ -984,12 +1015,16 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>Total,style="color:</t>
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
+Lu Gongchao,Submitted
+Xu Shirong,Submitted</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>未评分(工程师)</t>
+          <t>未确认(Cao Liang)</t>
         </is>
       </c>
       <c r="S6" t="inlineStr"/>
@@ -997,23 +1032,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>30036039-EBP</t>
+          <t>30033911-EBP</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>30036039-2026,AP,SERES Motors,L97-DAB, Lamination, 260171, 1T,Equipment</t>
+          <t>30033911-2026,NA,Stellantis,WL-DP,laminnation,260060,T,Equipment</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SERES Motors</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Stellantis</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Wang Xiang02_王翔(uwanx029)</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Huang Dongfang01_黄东方(uhuad056)</t>
+          <t>Jin Yulong01_金宇隆(ujiny132)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1028,12 +1067,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1043,28 +1082,34 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Phase 2 Gate Exit-DVR</t>
+          <t>Phase 4 Gate Exit-CPA</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t xml:space="preserve">最低打分：；
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：0；
+Lu Dinghao的PKR打分：100；
+Lu Gongchao的PKR打分：0；
+Xu Shirong的PKR打分：0；
 </t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>完成</t>
+          <t>Wang Hao23的PKR打分：0；
+Lu Gongchao的PKR打分：0；
+Xu Shirong的PKR打分：0；</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1074,7 +1119,11 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Total,style="color:</t>
+          <t>Total,Submitted
+Wang Hao23,style="color:
+Lu Dinghao,Submitted
+Lu Gongchao,style="color:
+Xu Shirong,style="color:</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1087,27 +1136,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>30035707-EBP</t>
+          <t>30036039-EBP</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>30035707-2026,AP,Brilliance-BMW,RGB 8PIN-light,assemble,260156,T,Equipment</t>
+          <t>30036039-2026,AP,SERES Motors,L97-DAB, Lamination, 260171, 1T,Equipment</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brilliance-BMW</t>
+          <t>SERES Motors</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Chen Jiarong_陈佳荣(uchej731)</t>
+          <t>Zou Chengcheng_邹成成(uzouc016)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Zhou Liwen_周理文(uzhol008)</t>
+          <t>Huang Dongfang01_黄东方(uhuad056)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1122,27 +1171,27 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1152,17 +1201,17 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t xml:space="preserve">最低打分：0；
+          <t xml:space="preserve">最低打分：100；
 Wang Hao23的PKR打分：100；
 Lu Dinghao的PKR打分：100；
+Lu Gongchao的PKR打分：100；
 Xu Shirong的PKR打分：100；
-Zhao Kailiang的PKR打分：0；
 </t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Zhao Kailiang的PKR打分：0；</t>
+          <t>完成</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1175,16 +1224,120 @@
           <t>Total,Submitted
 Wang Hao23,Submitted
 Lu Dinghao,Submitted
-Xu Shirong,Submitted
+Lu Gongchao,Submitted
+Xu Shirong,Submitted</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>未确认(Cao Liang)</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>30035707-EBP</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>30035707-2026,AP,Brilliance-BMW,RGB 8PIN-light,assemble,260156,T,Equipment</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Brilliance-BMW</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Chen Jiarong_陈佳荣(uchej731)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Zhou Liwen_周理文(uzhol008)</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Phase 1 Quotation</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Phase 3 Gate Exit-FPR</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：0；
+Lu Dinghao的PKR打分：100；
+Xu Shirong的PKR打分：0；
+Zhao Kailiang的PKR打分：0；
+</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Wang Hao23的PKR打分：0；
+Xu Shirong的PKR打分：0；
+Zhao Kailiang的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>本周</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,style="color:
+Lu Dinghao,Submitted
+Xu Shirong,style="color:
 Zhao Kailiang,style="color:</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>未评分(工程师)</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/yanfeng/PKR确认信息/PKR未完成情况（近两周）.xlsx
+++ b/yanfeng/PKR确认信息/PKR未完成情况（近两周）.xlsx
@@ -516,67 +516,67 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>30034171-EBP</t>
+          <t>30030313-EBP</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>30034171-2026,AP,Jianghuai,JHC-sun visor,assy, 260074, NT,Equipment</t>
+          <t>30030313-2026,AP,Tes,Highland-FC,Assembly,250268,3T,Equipment</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Jianghuai</t>
+          <t>Tes</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Wang Baowei_王保卫(uwanb363)</t>
+          <t>Gong Shengchao_龚胜超(ugons034)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Chen Zhibin01_陈志斌(uchez368)</t>
+          <t>Li Yanchen_李彦辰(ulixy466)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+          <t>Zhou Meijiao01_周美娇(uzhom121)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phase 4 Manufacturing Development</t>
+          <t>Phase 3 Design Feasibility</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Phase 4 Gate Exit-CPA</t>
+          <t>Phase 3 Gate Exit-FPR</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -584,16 +584,14 @@
           <t xml:space="preserve">最低打分：0；
 Wang Hao23的PKR打分：0；
 Lu Dinghao的PKR打分：100；
-Xu Shirong的PKR打分：0；
-Zhao Kailiang的PKR打分：0；
+Xu Shirong的PKR打分：100；
+Zhao Kailiang的PKR打分：100；
 </t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Wang Hao23的PKR打分：0；
-Xu Shirong的PKR打分：0；
-Zhao Kailiang的PKR打分：0；</t>
+          <t>Wang Hao23的PKR打分：0；</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -606,8 +604,8 @@
           <t>Total,Submitted
 Wang Hao23,style="color:
 Lu Dinghao,Submitted
-Xu Shirong,style="color:
-Zhao Kailiang,style="color:</t>
+Xu Shirong,Submitted
+Zhao Kailiang,Submitted</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -615,22 +613,26 @@
           <t>未评分(工程师)</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr"/>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>Gongchao.Lu@yanfeng.com; Hao.Wang23@yanfeng.com; Shirong.Xu@yanfeng.com</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>30034168-EBP</t>
+          <t>30034171-EBP</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>30034168-2026,AP,SVW,A-SUV-mirror,assembly,260008,15T,Equipment</t>
+          <t>30034171-2026,AP,Jianghuai,JHC-sun visor,assy, 260074, NT,Equipment</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SVW</t>
+          <t>Jianghuai</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -640,7 +642,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Zhou Liwen_周理文(uzhol008)</t>
+          <t>Chen Zhibin01_陈志斌(uchez368)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -650,7 +652,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phase 3 Design Feasibility</t>
+          <t>Phase 4 Manufacturing Development</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -675,7 +677,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -686,31 +688,30 @@
       <c r="N3" t="inlineStr">
         <is>
           <t xml:space="preserve">最低打分：0；
-Wang Hao23的PKR打分：100；
+Wang Hao23的PKR打分：0；
 Lu Dinghao的PKR打分：100；
-Xu Shirong的PKR打分：0；
-Zhao Kailiang的PKR打分：0；
+Xu Shirong的PKR打分：100；
+Zhao Kailiang的PKR打分：100；
 </t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Xu Shirong的PKR打分：0；
-Zhao Kailiang的PKR打分：0；</t>
+          <t>Wang Hao23的PKR打分：0；</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>下周</t>
+          <t>本周</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
           <t>Total,Submitted
-Wang Hao23,Submitted
+Wang Hao23,style="color:
 Lu Dinghao,Submitted
-Xu Shirong,style="color:
-Zhao Kailiang,style="color:</t>
+Xu Shirong,Submitted
+Zhao Kailiang,Submitted</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -723,34 +724,30 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>30034746-EBP</t>
+          <t>30034480-EBP</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>30034746-2026,AP,Huawei Anhui,X90-DP,260115,glue spray,M,Equipment</t>
+          <t>30034480-2028,AP,Toyota,780B,Spraying,260086,T,Equipment</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Huawei Anhui</t>
+          <t>Toyota</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Shang Bing_尚兵(ushab007)</t>
+          <t>Gong Shengchao_龚胜超(ugons034)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Cheng Debao_程德宝(uched025)</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Xu Shirong_徐时荣(uxuxs004)</t>
-        </is>
-      </c>
+          <t>Chen Ziyi01_陈子翌(uchez443)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>Phase 3 Design Feasibility</t>
@@ -758,27 +755,27 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>2026-05-24</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2026-05-23</t>
-        </is>
-      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2027-09-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -787,109 +784,6 @@
         </is>
       </c>
       <c r="N4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">最低打分：0；
-Wang Hao23的PKR打分：100；
-Lu Dinghao的PKR打分：100；
-Lu Gongchao的PKR打分：0；
-Xu Shirong的PKR打分：0；
-</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>Lu Gongchao的PKR打分：0；
-Xu Shirong的PKR打分：0；</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>下周</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>Total,Submitted
-Wang Hao23,Submitted
-Lu Dinghao,Submitted
-Lu Gongchao,style="color:
-Xu Shirong,style="color:</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>未评分(工程师)</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>30035162-EBP</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>30035162-2026,AP,BJEV,X90,Lamination,260133,M,Equipment</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>BJEV</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Shang Bing_尚兵(ushab007)</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Chen Jie04_陈洁(uchej018)</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Xu Shirong_徐时荣(uxuxs004)</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Phase 2 Concept Definition</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>2026-07-18</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>2027-10-20</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Phase 3 Gate Exit-FPR</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
         <is>
           <t xml:space="preserve">最低打分：0；
 Wang Hao23的PKR打分：0；
@@ -899,19 +793,19 @@
 </t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Wang Hao23的PKR打分：0；
 Lu Gongchao的PKR打分：0；
 Xu Shirong的PKR打分：0；</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>下周</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Total,Submitted
 Wang Hao23,style="color:
@@ -920,182 +814,76 @@
 Xu Shirong,style="color:</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>未评分(工程师)</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>30033911-EBP</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>30033911-2026,NA,Stellantis,WL-DP,laminnation,260060,T,Equipment</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Stellantis</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Wang Xiang02_王翔(uwanx029)</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Jin Yulong01_金宇隆(ujiny132)</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Xu Shirong_徐时荣(uxuxs004)</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Phase 1 Quotation</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>2026-12-31</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>Phase 2 Gate Exit-DVR</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">最低打分：100；
-Wang Hao23的PKR打分：100；
-Lu Dinghao的PKR打分：100；
-Lu Gongchao的PKR打分：100；
-Xu Shirong的PKR打分：100；
-</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>完成</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>本周</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>Total,Submitted
-Wang Hao23,Submitted
-Lu Dinghao,Submitted
-Lu Gongchao,Submitted
-Xu Shirong,Submitted</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>未确认(Cao Liang)</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>30033911-EBP</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>30033911-2026,NA,Stellantis,WL-DP,laminnation,260060,T,Equipment</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Stellantis</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Wang Xiang02_王翔(uwanx029)</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Jin Yulong01_金宇隆(ujiny132)</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Xu Shirong_徐时荣(uxuxs004)</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Phase 1 Quotation</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>2026-12-31</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>30034479-EBP</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>30034479-2027,AP,Toyota,780B,Spraying,260085,M,Equipment</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Toyota</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Gong Shengchao_龚胜超(ugons034)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Chen Jie04_陈洁(uchej018)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Phase 2 Concept Definition</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
         <is>
           <t>Phase 4 Gate Exit-CPA</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t xml:space="preserve">最低打分：0；
 Wang Hao23的PKR打分：0；
@@ -1105,19 +893,19 @@
 </t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Wang Hao23的PKR打分：0；
 Lu Gongchao的PKR打分：0；
 Xu Shirong的PKR打分：0；</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>本周</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Total,Submitted
 Wang Hao23,style="color:
@@ -1126,6 +914,207 @@
 Xu Shirong,style="color:</t>
         </is>
       </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>30034477-EBP</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>30034477-2025,AP,Toyota,780B-DP,Flaming, 260079,M,Equipment</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Toyota</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Gong Shengchao_龚胜超(ugons034)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Huang Linjian_黄琳健(uhual254)</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Phase 3 Design Feasibility</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Phase 4 Gate Exit-CPA</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：0；
+Lu Dinghao的PKR打分：100；
+Xu Shirong的PKR打分：0；
+Zhao Kailiang的PKR打分：100；
+</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Wang Hao23的PKR打分：0；
+Xu Shirong的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,style="color:
+Lu Dinghao,Submitted
+Xu Shirong,style="color:
+Zhao Kailiang,Submitted</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>30035162-EBP</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>30035162-2026,AP,BJEV,X90,Lamination,260133,M,Equipment</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>BJEV</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Shang Bing_尚兵(ushab007)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Chen Jie04_陈洁(uchej018)</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Phase 2 Concept Definition</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>2027-10-20</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Phase 3 Gate Exit-FPR</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：0；
+Lu Dinghao的PKR打分：100；
+Lu Gongchao的PKR打分：100；
+Xu Shirong的PKR打分：100；
+</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Wang Hao23的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>本周</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,style="color:
+Lu Dinghao,Submitted
+Lu Gongchao,Submitted
+Xu Shirong,Submitted</t>
+        </is>
+      </c>
       <c r="R7" t="inlineStr">
         <is>
           <t>未评分(工程师)</t>
@@ -1136,27 +1125,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>30036039-EBP</t>
+          <t>30036184-EBP</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>30036039-2026,AP,SERES Motors,L97-DAB, Lamination, 260171, 1T,Equipment</t>
+          <t>30036184-2026,AP,JAC-VW,JHB-sunvisor,assem, 260180, 2T,Equipment</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SERES Motors</t>
+          <t>JAC-VW</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Zou Chengcheng_邹成成(uzouc016)</t>
+          <t>Wang Baowei_王保卫(uwanb363)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Huang Dongfang01_黄东方(uhuad056)</t>
+          <t>Chen Zhibin01_陈志斌(uchez368)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1166,71 +1155,72 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phase 1 Quotation</t>
+          <t>Phase 2 Concept Definition</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Phase 2 Gate Exit-DVR</t>
+          <t>Phase 3 Gate Exit-FPR</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t xml:space="preserve">最低打分：100；
-Wang Hao23的PKR打分：100；
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：0；
 Lu Dinghao的PKR打分：100；
-Lu Gongchao的PKR打分：100；
-Xu Shirong的PKR打分：100；
+Xu Shirong的PKR打分：0；
+Zhao Kailiang的PKR打分：100；
 </t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>完成</t>
+          <t>Wang Hao23的PKR打分：0；
+Xu Shirong的PKR打分：0；</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>本周</t>
+          <t>下周</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
           <t>Total,Submitted
-Wang Hao23,Submitted
+Wang Hao23,style="color:
 Lu Dinghao,Submitted
-Lu Gongchao,Submitted
-Xu Shirong,Submitted</t>
+Xu Shirong,style="color:
+Zhao Kailiang,Submitted</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>未确认(Cao Liang)</t>
+          <t>未评分(工程师)</t>
         </is>
       </c>
       <c r="S8" t="inlineStr"/>
@@ -1306,16 +1296,14 @@
           <t xml:space="preserve">最低打分：0；
 Wang Hao23的PKR打分：0；
 Lu Dinghao的PKR打分：100；
-Xu Shirong的PKR打分：0；
-Zhao Kailiang的PKR打分：0；
+Xu Shirong的PKR打分：100；
+Zhao Kailiang的PKR打分：100；
 </t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Wang Hao23的PKR打分：0；
-Xu Shirong的PKR打分：0；
-Zhao Kailiang的PKR打分：0；</t>
+          <t>Wang Hao23的PKR打分：0；</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1328,8 +1316,8 @@
           <t>Total,Submitted
 Wang Hao23,style="color:
 Lu Dinghao,Submitted
-Xu Shirong,style="color:
-Zhao Kailiang,style="color:</t>
+Xu Shirong,Submitted
+Zhao Kailiang,Submitted</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
